--- a/12-02/Лист Microsoft Excel.xlsx
+++ b/12-02/Лист Microsoft Excel.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -11,13 +11,141 @@
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211" fullCalcOnLoad="1"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">SELECT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TABLE_NAME as "Название таблицы",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    GROUP_CONCAT(COLUMN_NAME ORDER BY ORDINAL_POSITION) as "Название первичного ключа"</t>
+  </si>
+  <si>
+    <t>FROM INFORMATION_SCHEMA.KEY_COLUMN_USAGE</t>
+  </si>
+  <si>
+    <t>WHERE TABLE_SCHEMA = 'sakila'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AND CONSTRAINT_NAME = 'PRIMARY'</t>
+  </si>
+  <si>
+    <t>GROUP BY TABLE_NAME</t>
+  </si>
+  <si>
+    <t>ORDER BY TABLE_NAME</t>
+  </si>
+  <si>
+    <t>Название таблицы</t>
+  </si>
+  <si>
+    <t>Название первичного ключа</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>actor_id</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>address_id</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>category_id</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>city_id</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>country_id</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>film</t>
+  </si>
+  <si>
+    <t>film_id</t>
+  </si>
+  <si>
+    <t>film_actor</t>
+  </si>
+  <si>
+    <t>actor_id,film_id</t>
+  </si>
+  <si>
+    <t>film_category</t>
+  </si>
+  <si>
+    <t>film_id,category_id</t>
+  </si>
+  <si>
+    <t>film_text</t>
+  </si>
+  <si>
+    <t>inventory</t>
+  </si>
+  <si>
+    <t>inventory_id</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>language_id</t>
+  </si>
+  <si>
+    <t>payment</t>
+  </si>
+  <si>
+    <t>payment_id</t>
+  </si>
+  <si>
+    <t>rental</t>
+  </si>
+  <si>
+    <t>rental_id</t>
+  </si>
+  <si>
+    <t>staff</t>
+  </si>
+  <si>
+    <t>staff_id</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>store_id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -25,16 +153,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E3FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -42,25 +205,190 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF6495ED"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF6495ED"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF6495ED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF6495ED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6495ED"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6495ED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6495ED"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6495ED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6495ED"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF6495ED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6495ED"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF6495ED"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6495ED"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF6495ED"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -98,7 +426,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -170,7 +498,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -343,27 +671,224 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+    </row>
+    <row r="10" spans="1:2" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:B9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
